--- a/rules/CORE-000723/negative/01/data/unit-test-coreid-FB0907-negative.xlsx
+++ b/rules/CORE-000723/negative/01/data/unit-test-coreid-FB0907-negative.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="cm.xpt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="mh.xpt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ae.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mh.xpt" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,7 +43,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,6 +148,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -612,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +654,322 @@
         <is>
           <t>Error value</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AEHLT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Headaches NEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AEHLTCD</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>10019233</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AEHLT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Headaches NEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AEHLTCD</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>10019234</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AEHLT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Headaches NEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AEHLTCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AEHLT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Headaches NEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AEHLTCD</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>10019233</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AEHLT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vascular hypertensive disorders NEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AEHLTCD</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>10020774</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AEHLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AEHLTCD</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>10020774</v>
       </c>
     </row>
   </sheetData>
@@ -1467,12 +1792,12 @@
       <c r="J6" s="9" t="n">
         <v>10019211</v>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>Headaches NEC</t>
         </is>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="14" t="n">
         <v>10019233</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
@@ -1608,12 +1933,12 @@
       <c r="J7" s="9" t="n">
         <v>10019211</v>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t>Headaches NEC</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t>10019234</t>
         </is>
@@ -1751,12 +2076,12 @@
       <c r="J8" s="9" t="n">
         <v>10019211</v>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="K8" s="14" t="inlineStr">
         <is>
           <t>Headaches NEC</t>
         </is>
       </c>
-      <c r="L8" s="11" t="n"/>
+      <c r="L8" s="14" t="n"/>
       <c r="M8" s="9" t="inlineStr">
         <is>
           <t>Headaches</t>
@@ -1890,12 +2215,12 @@
       <c r="J9" s="9" t="n">
         <v>10019211</v>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t>Headaches NEC</t>
         </is>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="14" t="n">
         <v>10019233</v>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -2031,12 +2356,12 @@
       <c r="J10" s="9" t="n">
         <v>10020772</v>
       </c>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="K10" s="14" t="inlineStr">
         <is>
           <t>Vascular hypertensive disorders NEC</t>
         </is>
       </c>
-      <c r="L10" s="13" t="n">
+      <c r="L10" s="14" t="n">
         <v>10020774</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
@@ -2172,8 +2497,8 @@
       <c r="J11" s="9" t="n">
         <v>10020772</v>
       </c>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="13" t="n">
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n">
         <v>10020774</v>
       </c>
       <c r="M11" s="9" t="inlineStr">
@@ -7414,7 +7739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7465,55 +7790,45 @@
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>MHHLT</t>
+          <t>MHHLGT</t>
         </is>
       </c>
       <c r="K1" s="5" t="inlineStr">
         <is>
-          <t>MHHLTCD</t>
+          <t>MHHLGTCD</t>
         </is>
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
-          <t>MHHLGT</t>
+          <t>MHBODSYS</t>
         </is>
       </c>
       <c r="M1" s="5" t="inlineStr">
         <is>
-          <t>MHHLGTCD</t>
+          <t>MHBDSYCD</t>
         </is>
       </c>
       <c r="N1" s="5" t="inlineStr">
         <is>
-          <t>MHBODSYS</t>
+          <t>MHSOC</t>
         </is>
       </c>
       <c r="O1" s="5" t="inlineStr">
         <is>
-          <t>MHBDSYCD</t>
+          <t>MHSOCCD</t>
         </is>
       </c>
       <c r="P1" s="5" t="inlineStr">
         <is>
-          <t>MHSOC</t>
+          <t>MHEVDTYP</t>
         </is>
       </c>
       <c r="Q1" s="5" t="inlineStr">
         <is>
-          <t>MHSOCCD</t>
+          <t>MHSTDTC</t>
         </is>
       </c>
       <c r="R1" s="5" t="inlineStr">
-        <is>
-          <t>MHEVDTYP</t>
-        </is>
-      </c>
-      <c r="S1" s="5" t="inlineStr">
-        <is>
-          <t>MHSTDTC</t>
-        </is>
-      </c>
-      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>MHSTDY</t>
         </is>
@@ -7567,55 +7882,45 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>High Level Term</t>
+          <t>High Level Group Term</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>High Level Term Code</t>
+          <t>High Level Group Term Code</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>High Level Group Term</t>
+          <t>Body System or Organ Class</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>High Level Group Term Code</t>
+          <t>Body System or Organ Class Code</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>Body System or Organ Class</t>
+          <t>Primary System Organ Class</t>
         </is>
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>Body System or Organ Class Code</t>
+          <t>Primary System Organ Class Code</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
         <is>
-          <t>Primary System Organ Class</t>
+          <t>Medical History Event Date Type</t>
         </is>
       </c>
       <c r="Q2" s="7" t="inlineStr">
         <is>
-          <t>Primary System Organ Class Code</t>
+          <t>Start Date/Time of Medical History Event</t>
         </is>
       </c>
       <c r="R2" s="7" t="inlineStr">
-        <is>
-          <t>Medical History Event Date Type</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>Start Date/Time of Medical History Event</t>
-        </is>
-      </c>
-      <c r="T2" s="7" t="inlineStr">
         <is>
           <t>Study Day of Start of Observation</t>
         </is>
@@ -7704,20 +8009,10 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>Num</t>
+          <t>Char</t>
         </is>
       </c>
       <c r="R3" s="7" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="T3" s="7" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
@@ -7752,13 +8047,13 @@
         <v>8</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>8</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>8</v>
@@ -7770,18 +8065,12 @@
         <v>8</v>
       </c>
       <c r="P4" s="7" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="S4" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" s="7" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7829,24 +8118,24 @@
           <t>10012271</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>Alzheimer's disease (incl subtypes)</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>10001897</t>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Mental impairment disorders</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>10057167</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>Mental impairment disorders</t>
+          <t>Nervous system disorders</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>10057167</t>
+          <t>10029205</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
@@ -7861,25 +8150,15 @@
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>Nervous system disorders</t>
+          <t>SYMPTOM ONSET</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>10029205</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>SYMPTOM ONSET</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
           <t>2004-05-28</t>
         </is>
       </c>
-      <c r="T5" s="9" t="n">
+      <c r="R5" s="9" t="n">
         <v>-3108</v>
       </c>
     </row>
@@ -7927,24 +8206,24 @@
           <t>10012271</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>Alzheimer's disease (incl subtypes)</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>10001898</t>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Mental impairment disorders</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>10057167</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>Mental impairment disorders</t>
+          <t>Nervous system disorders</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>10057167</t>
+          <t>10029205</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
@@ -7959,25 +8238,15 @@
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>Nervous system disorders</t>
+          <t>SYMPTOM ONSET</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>10029205</t>
-        </is>
-      </c>
-      <c r="R6" s="9" t="inlineStr">
-        <is>
-          <t>SYMPTOM ONSET</t>
-        </is>
-      </c>
-      <c r="S6" s="9" t="inlineStr">
-        <is>
           <t>2010-03-19</t>
         </is>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="R6" s="9" t="n">
         <v>-972</v>
       </c>
     </row>
@@ -8025,20 +8294,24 @@
           <t>10012271</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>Alzheimer's disease (incl subtypes)</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="n"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Mental impairment disorders</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>10057167</t>
+        </is>
+      </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>Mental impairment disorders</t>
+          <t>Nervous system disorders</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>10057167</t>
+          <t>10029205</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -8053,25 +8326,15 @@
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>Nervous system disorders</t>
+          <t>SYMPTOM ONSET</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>10029205</t>
-        </is>
-      </c>
-      <c r="R7" s="9" t="inlineStr">
-        <is>
-          <t>SYMPTOM ONSET</t>
-        </is>
-      </c>
-      <c r="S7" s="9" t="inlineStr">
-        <is>
           <t>2007-02-09</t>
         </is>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="R7" s="9" t="n">
         <v>-2393</v>
       </c>
     </row>
@@ -8119,24 +8382,24 @@
           <t>10012271</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Alzheimer's disease (incl subtype)</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>10001897</t>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Mental impairment disorders</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>10057167</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>Mental impairment disorders</t>
+          <t>Nervous system disorders</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>10057167</t>
+          <t>10029205</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -8151,25 +8414,15 @@
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>Nervous system disorders</t>
+          <t>SYMPTOM ONSET</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>10029205</t>
-        </is>
-      </c>
-      <c r="R8" s="9" t="inlineStr">
-        <is>
-          <t>SYMPTOM ONSET</t>
-        </is>
-      </c>
-      <c r="S8" s="9" t="inlineStr">
-        <is>
           <t>2010-11-05</t>
         </is>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="R8" s="9" t="n">
         <v>-1068</v>
       </c>
     </row>
@@ -8217,24 +8470,24 @@
           <t>10012271</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>Alzheimer's disease (incl subtype)</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>10001898</t>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Mental impairment disorders</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>10057167</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>Mental impairment disorders</t>
+          <t>Nervous system disorders</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>10057167</t>
+          <t>10029205</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
@@ -8249,25 +8502,15 @@
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>Nervous system disorders</t>
+          <t>SYMPTOM ONSET</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>10029205</t>
-        </is>
-      </c>
-      <c r="R9" s="9" t="inlineStr">
-        <is>
-          <t>SYMPTOM ONSET</t>
-        </is>
-      </c>
-      <c r="S9" s="9" t="inlineStr">
-        <is>
           <t>2006-08-20</t>
         </is>
       </c>
-      <c r="T9" s="9" t="n">
+      <c r="R9" s="9" t="n">
         <v>-2360</v>
       </c>
     </row>
